--- a/public/plantilla-contratistas.xlsx
+++ b/public/plantilla-contratistas.xlsx
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="40">
+  <numFmts count="0"/>
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -301,6 +302,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1029,7 +1034,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="364">
+  <cellXfs count="374">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1945,6 +1950,40 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2665,16 +2704,16 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="93" t="n"/>
-      <c r="J11" s="93" t="n"/>
-      <c r="K11" s="93" t="n"/>
-      <c r="L11" s="89" t="n"/>
+      <c r="C11" s="364" t="n"/>
+      <c r="D11" s="365" t="n"/>
+      <c r="E11" s="365" t="n"/>
+      <c r="F11" s="365" t="n"/>
+      <c r="G11" s="365" t="n"/>
+      <c r="H11" s="365" t="n"/>
+      <c r="I11" s="365" t="n"/>
+      <c r="J11" s="365" t="n"/>
+      <c r="K11" s="365" t="n"/>
+      <c r="L11" s="366" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2683,20 +2722,20 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="364" t="n"/>
+      <c r="D12" s="365" t="n"/>
+      <c r="E12" s="365" t="n"/>
+      <c r="F12" s="365" t="n"/>
+      <c r="G12" s="366" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>NIT</t>
         </is>
       </c>
       <c r="I12" s="89" t="n"/>
-      <c r="J12" s="68" t="n"/>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="89" t="n"/>
+      <c r="J12" s="364" t="n"/>
+      <c r="K12" s="365" t="n"/>
+      <c r="L12" s="366" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2705,20 +2744,20 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="68" t="n"/>
-      <c r="D13" s="93" t="n"/>
-      <c r="E13" s="93" t="n"/>
-      <c r="F13" s="93" t="n"/>
-      <c r="G13" s="89" t="n"/>
+      <c r="C13" s="364" t="n"/>
+      <c r="D13" s="365" t="n"/>
+      <c r="E13" s="365" t="n"/>
+      <c r="F13" s="365" t="n"/>
+      <c r="G13" s="366" t="n"/>
       <c r="H13" s="59" t="inlineStr">
         <is>
           <t>Teléfono</t>
         </is>
       </c>
       <c r="I13" s="89" t="n"/>
-      <c r="J13" s="68" t="n"/>
-      <c r="K13" s="93" t="n"/>
-      <c r="L13" s="89" t="n"/>
+      <c r="J13" s="364" t="n"/>
+      <c r="K13" s="365" t="n"/>
+      <c r="L13" s="366" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="127">
       <c r="A14" s="59" t="inlineStr">
@@ -2727,16 +2766,16 @@
         </is>
       </c>
       <c r="B14" s="89" t="n"/>
-      <c r="C14" s="68" t="n"/>
-      <c r="D14" s="93" t="n"/>
-      <c r="E14" s="93" t="n"/>
-      <c r="F14" s="93" t="n"/>
-      <c r="G14" s="93" t="n"/>
-      <c r="H14" s="93" t="n"/>
-      <c r="I14" s="93" t="n"/>
-      <c r="J14" s="93" t="n"/>
-      <c r="K14" s="93" t="n"/>
-      <c r="L14" s="89" t="n"/>
+      <c r="C14" s="364" t="n"/>
+      <c r="D14" s="365" t="n"/>
+      <c r="E14" s="365" t="n"/>
+      <c r="F14" s="365" t="n"/>
+      <c r="G14" s="365" t="n"/>
+      <c r="H14" s="365" t="n"/>
+      <c r="I14" s="365" t="n"/>
+      <c r="J14" s="365" t="n"/>
+      <c r="K14" s="365" t="n"/>
+      <c r="L14" s="366" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="127">
       <c r="A15" s="59" t="inlineStr">
@@ -2745,24 +2784,24 @@
         </is>
       </c>
       <c r="B15" s="89" t="n"/>
-      <c r="C15" s="69" t="n"/>
-      <c r="D15" s="89" t="n"/>
+      <c r="C15" s="367" t="n"/>
+      <c r="D15" s="366" t="n"/>
       <c r="E15" s="59" t="inlineStr">
         <is>
           <t>Periodo evaluado</t>
         </is>
       </c>
       <c r="F15" s="89" t="n"/>
-      <c r="G15" s="69" t="n"/>
-      <c r="H15" s="89" t="n"/>
+      <c r="G15" s="367" t="n"/>
+      <c r="H15" s="366" t="n"/>
       <c r="I15" s="59" t="inlineStr">
         <is>
           <t>Trabajadores del contratista</t>
         </is>
       </c>
       <c r="J15" s="89" t="n"/>
-      <c r="K15" s="69" t="n"/>
-      <c r="L15" s="89" t="n"/>
+      <c r="K15" s="367" t="n"/>
+      <c r="L15" s="366" t="n"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="127">
       <c r="A16" s="137" t="inlineStr">
@@ -2813,10 +2852,10 @@
       <c r="L17" s="348" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1" s="127">
-      <c r="A18" s="306" t="n">
+      <c r="A18" s="368" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="230" t="inlineStr">
+      <c r="B18" s="369" t="inlineStr">
         <is>
           <t>Todos los trabajadores afiliados a ARL, EPS y pensión</t>
         </is>
@@ -2826,17 +2865,17 @@
       <c r="E18" s="98" t="n"/>
       <c r="F18" s="98" t="n"/>
       <c r="G18" s="97" t="n"/>
-      <c r="H18" s="306" t="n"/>
-      <c r="I18" s="97" t="n"/>
-      <c r="J18" s="230" t="n"/>
-      <c r="K18" s="98" t="n"/>
-      <c r="L18" s="97" t="n"/>
+      <c r="H18" s="370" t="n"/>
+      <c r="I18" s="371" t="n"/>
+      <c r="J18" s="372" t="n"/>
+      <c r="K18" s="373" t="n"/>
+      <c r="L18" s="371" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1" s="127">
-      <c r="A19" s="306" t="n">
+      <c r="A19" s="368" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="230" t="inlineStr">
+      <c r="B19" s="369" t="inlineStr">
         <is>
           <t>Pago de la seguridad social al día (planilla)</t>
         </is>
@@ -2846,17 +2885,17 @@
       <c r="E19" s="98" t="n"/>
       <c r="F19" s="98" t="n"/>
       <c r="G19" s="97" t="n"/>
-      <c r="H19" s="306" t="n"/>
-      <c r="I19" s="97" t="n"/>
-      <c r="J19" s="230" t="n"/>
-      <c r="K19" s="98" t="n"/>
-      <c r="L19" s="97" t="n"/>
+      <c r="H19" s="370" t="n"/>
+      <c r="I19" s="371" t="n"/>
+      <c r="J19" s="372" t="n"/>
+      <c r="K19" s="373" t="n"/>
+      <c r="L19" s="371" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1" s="127">
-      <c r="A20" s="306" t="n">
+      <c r="A20" s="368" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="230" t="inlineStr">
+      <c r="B20" s="369" t="inlineStr">
         <is>
           <t>Responsable del SG-SST con licencia vigente</t>
         </is>
@@ -2866,17 +2905,17 @@
       <c r="E20" s="98" t="n"/>
       <c r="F20" s="98" t="n"/>
       <c r="G20" s="97" t="n"/>
-      <c r="H20" s="306" t="n"/>
-      <c r="I20" s="97" t="n"/>
-      <c r="J20" s="230" t="n"/>
-      <c r="K20" s="98" t="n"/>
-      <c r="L20" s="97" t="n"/>
+      <c r="H20" s="370" t="n"/>
+      <c r="I20" s="371" t="n"/>
+      <c r="J20" s="372" t="n"/>
+      <c r="K20" s="373" t="n"/>
+      <c r="L20" s="371" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1" s="127">
-      <c r="A21" s="306" t="n">
+      <c r="A21" s="368" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="230" t="inlineStr">
+      <c r="B21" s="369" t="inlineStr">
         <is>
           <t>Política de SST firmada y divulgada</t>
         </is>
@@ -2886,17 +2925,17 @@
       <c r="E21" s="98" t="n"/>
       <c r="F21" s="98" t="n"/>
       <c r="G21" s="97" t="n"/>
-      <c r="H21" s="306" t="n"/>
-      <c r="I21" s="97" t="n"/>
-      <c r="J21" s="230" t="n"/>
-      <c r="K21" s="98" t="n"/>
-      <c r="L21" s="97" t="n"/>
+      <c r="H21" s="370" t="n"/>
+      <c r="I21" s="371" t="n"/>
+      <c r="J21" s="372" t="n"/>
+      <c r="K21" s="373" t="n"/>
+      <c r="L21" s="371" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1" s="127">
-      <c r="A22" s="306" t="n">
+      <c r="A22" s="368" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="230" t="inlineStr">
+      <c r="B22" s="369" t="inlineStr">
         <is>
           <t>Matriz de peligros y valoración de riesgos</t>
         </is>
@@ -2906,17 +2945,17 @@
       <c r="E22" s="98" t="n"/>
       <c r="F22" s="98" t="n"/>
       <c r="G22" s="97" t="n"/>
-      <c r="H22" s="306" t="n"/>
-      <c r="I22" s="97" t="n"/>
-      <c r="J22" s="230" t="n"/>
-      <c r="K22" s="98" t="n"/>
-      <c r="L22" s="97" t="n"/>
+      <c r="H22" s="370" t="n"/>
+      <c r="I22" s="371" t="n"/>
+      <c r="J22" s="372" t="n"/>
+      <c r="K22" s="373" t="n"/>
+      <c r="L22" s="371" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1" s="127">
-      <c r="A23" s="306" t="n">
+      <c r="A23" s="368" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="230" t="inlineStr">
+      <c r="B23" s="369" t="inlineStr">
         <is>
           <t>Plan anual de trabajo del SG-SST</t>
         </is>
@@ -2926,17 +2965,17 @@
       <c r="E23" s="98" t="n"/>
       <c r="F23" s="98" t="n"/>
       <c r="G23" s="97" t="n"/>
-      <c r="H23" s="306" t="n"/>
-      <c r="I23" s="97" t="n"/>
-      <c r="J23" s="230" t="n"/>
-      <c r="K23" s="98" t="n"/>
-      <c r="L23" s="97" t="n"/>
+      <c r="H23" s="370" t="n"/>
+      <c r="I23" s="371" t="n"/>
+      <c r="J23" s="372" t="n"/>
+      <c r="K23" s="373" t="n"/>
+      <c r="L23" s="371" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1" s="127">
-      <c r="A24" s="306" t="n">
+      <c r="A24" s="368" t="n">
         <v>7</v>
       </c>
-      <c r="B24" s="230" t="inlineStr">
+      <c r="B24" s="369" t="inlineStr">
         <is>
           <t>Exámenes médicos ocupacionales de ingreso</t>
         </is>
@@ -2946,17 +2985,17 @@
       <c r="E24" s="98" t="n"/>
       <c r="F24" s="98" t="n"/>
       <c r="G24" s="97" t="n"/>
-      <c r="H24" s="306" t="n"/>
-      <c r="I24" s="97" t="n"/>
-      <c r="J24" s="230" t="n"/>
-      <c r="K24" s="98" t="n"/>
-      <c r="L24" s="97" t="n"/>
+      <c r="H24" s="370" t="n"/>
+      <c r="I24" s="371" t="n"/>
+      <c r="J24" s="372" t="n"/>
+      <c r="K24" s="373" t="n"/>
+      <c r="L24" s="371" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1" s="127">
-      <c r="A25" s="306" t="n">
+      <c r="A25" s="368" t="n">
         <v>8</v>
       </c>
-      <c r="B25" s="230" t="inlineStr">
+      <c r="B25" s="369" t="inlineStr">
         <is>
           <t>Inducción en SST a todo el personal</t>
         </is>
@@ -2966,17 +3005,17 @@
       <c r="E25" s="98" t="n"/>
       <c r="F25" s="98" t="n"/>
       <c r="G25" s="97" t="n"/>
-      <c r="H25" s="306" t="n"/>
-      <c r="I25" s="97" t="n"/>
-      <c r="J25" s="230" t="n"/>
-      <c r="K25" s="98" t="n"/>
-      <c r="L25" s="97" t="n"/>
+      <c r="H25" s="370" t="n"/>
+      <c r="I25" s="371" t="n"/>
+      <c r="J25" s="372" t="n"/>
+      <c r="K25" s="373" t="n"/>
+      <c r="L25" s="371" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1" s="127">
-      <c r="A26" s="306" t="n">
+      <c r="A26" s="368" t="n">
         <v>9</v>
       </c>
-      <c r="B26" s="230" t="inlineStr">
+      <c r="B26" s="369" t="inlineStr">
         <is>
           <t>Certificados vigentes de trabajo en alturas y demás competencias</t>
         </is>
@@ -2986,17 +3025,17 @@
       <c r="E26" s="98" t="n"/>
       <c r="F26" s="98" t="n"/>
       <c r="G26" s="97" t="n"/>
-      <c r="H26" s="306" t="n"/>
-      <c r="I26" s="97" t="n"/>
-      <c r="J26" s="230" t="n"/>
-      <c r="K26" s="98" t="n"/>
-      <c r="L26" s="97" t="n"/>
+      <c r="H26" s="370" t="n"/>
+      <c r="I26" s="371" t="n"/>
+      <c r="J26" s="372" t="n"/>
+      <c r="K26" s="373" t="n"/>
+      <c r="L26" s="371" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1" s="127">
-      <c r="A27" s="306" t="n">
+      <c r="A27" s="368" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="230" t="inlineStr">
+      <c r="B27" s="369" t="inlineStr">
         <is>
           <t>Entrega y uso de EPP, con registro</t>
         </is>
@@ -3006,17 +3045,17 @@
       <c r="E27" s="98" t="n"/>
       <c r="F27" s="98" t="n"/>
       <c r="G27" s="97" t="n"/>
-      <c r="H27" s="306" t="n"/>
-      <c r="I27" s="97" t="n"/>
-      <c r="J27" s="230" t="n"/>
-      <c r="K27" s="98" t="n"/>
-      <c r="L27" s="97" t="n"/>
+      <c r="H27" s="370" t="n"/>
+      <c r="I27" s="371" t="n"/>
+      <c r="J27" s="372" t="n"/>
+      <c r="K27" s="373" t="n"/>
+      <c r="L27" s="371" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1" s="127">
-      <c r="A28" s="306" t="n">
+      <c r="A28" s="368" t="n">
         <v>11</v>
       </c>
-      <c r="B28" s="230" t="inlineStr">
+      <c r="B28" s="369" t="inlineStr">
         <is>
           <t>ATS y permisos de trabajo de alto riesgo</t>
         </is>
@@ -3026,17 +3065,17 @@
       <c r="E28" s="98" t="n"/>
       <c r="F28" s="98" t="n"/>
       <c r="G28" s="97" t="n"/>
-      <c r="H28" s="306" t="n"/>
-      <c r="I28" s="97" t="n"/>
-      <c r="J28" s="230" t="n"/>
-      <c r="K28" s="98" t="n"/>
-      <c r="L28" s="97" t="n"/>
+      <c r="H28" s="370" t="n"/>
+      <c r="I28" s="371" t="n"/>
+      <c r="J28" s="372" t="n"/>
+      <c r="K28" s="373" t="n"/>
+      <c r="L28" s="371" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1" s="127">
-      <c r="A29" s="306" t="n">
+      <c r="A29" s="368" t="n">
         <v>12</v>
       </c>
-      <c r="B29" s="230" t="inlineStr">
+      <c r="B29" s="369" t="inlineStr">
         <is>
           <t>Inspecciones de seguridad documentadas</t>
         </is>
@@ -3046,17 +3085,17 @@
       <c r="E29" s="98" t="n"/>
       <c r="F29" s="98" t="n"/>
       <c r="G29" s="97" t="n"/>
-      <c r="H29" s="306" t="n"/>
-      <c r="I29" s="97" t="n"/>
-      <c r="J29" s="230" t="n"/>
-      <c r="K29" s="98" t="n"/>
-      <c r="L29" s="97" t="n"/>
+      <c r="H29" s="370" t="n"/>
+      <c r="I29" s="371" t="n"/>
+      <c r="J29" s="372" t="n"/>
+      <c r="K29" s="373" t="n"/>
+      <c r="L29" s="371" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1" s="127">
-      <c r="A30" s="306" t="n">
+      <c r="A30" s="368" t="n">
         <v>13</v>
       </c>
-      <c r="B30" s="230" t="inlineStr">
+      <c r="B30" s="369" t="inlineStr">
         <is>
           <t>Equipos y herramientas en buen estado (inspección preoperacional)</t>
         </is>
@@ -3066,17 +3105,17 @@
       <c r="E30" s="98" t="n"/>
       <c r="F30" s="98" t="n"/>
       <c r="G30" s="97" t="n"/>
-      <c r="H30" s="306" t="n"/>
-      <c r="I30" s="97" t="n"/>
-      <c r="J30" s="230" t="n"/>
-      <c r="K30" s="98" t="n"/>
-      <c r="L30" s="97" t="n"/>
+      <c r="H30" s="370" t="n"/>
+      <c r="I30" s="371" t="n"/>
+      <c r="J30" s="372" t="n"/>
+      <c r="K30" s="373" t="n"/>
+      <c r="L30" s="371" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1" s="127">
-      <c r="A31" s="306" t="n">
+      <c r="A31" s="368" t="n">
         <v>14</v>
       </c>
-      <c r="B31" s="230" t="inlineStr">
+      <c r="B31" s="369" t="inlineStr">
         <is>
           <t>Señalización, orden y aseo en el frente de trabajo</t>
         </is>
@@ -3086,17 +3125,17 @@
       <c r="E31" s="98" t="n"/>
       <c r="F31" s="98" t="n"/>
       <c r="G31" s="97" t="n"/>
-      <c r="H31" s="306" t="n"/>
-      <c r="I31" s="97" t="n"/>
-      <c r="J31" s="230" t="n"/>
-      <c r="K31" s="98" t="n"/>
-      <c r="L31" s="97" t="n"/>
+      <c r="H31" s="370" t="n"/>
+      <c r="I31" s="371" t="n"/>
+      <c r="J31" s="372" t="n"/>
+      <c r="K31" s="373" t="n"/>
+      <c r="L31" s="371" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1" s="127">
-      <c r="A32" s="306" t="n">
+      <c r="A32" s="368" t="n">
         <v>15</v>
       </c>
-      <c r="B32" s="230" t="inlineStr">
+      <c r="B32" s="369" t="inlineStr">
         <is>
           <t>Plan de emergencias y brigada conformada</t>
         </is>
@@ -3106,17 +3145,17 @@
       <c r="E32" s="98" t="n"/>
       <c r="F32" s="98" t="n"/>
       <c r="G32" s="97" t="n"/>
-      <c r="H32" s="306" t="n"/>
-      <c r="I32" s="97" t="n"/>
-      <c r="J32" s="230" t="n"/>
-      <c r="K32" s="98" t="n"/>
-      <c r="L32" s="97" t="n"/>
+      <c r="H32" s="370" t="n"/>
+      <c r="I32" s="371" t="n"/>
+      <c r="J32" s="372" t="n"/>
+      <c r="K32" s="373" t="n"/>
+      <c r="L32" s="371" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1" s="127">
-      <c r="A33" s="306" t="n">
+      <c r="A33" s="368" t="n">
         <v>16</v>
       </c>
-      <c r="B33" s="230" t="inlineStr">
+      <c r="B33" s="369" t="inlineStr">
         <is>
           <t>Botiquín y extintores disponibles</t>
         </is>
@@ -3126,17 +3165,17 @@
       <c r="E33" s="98" t="n"/>
       <c r="F33" s="98" t="n"/>
       <c r="G33" s="97" t="n"/>
-      <c r="H33" s="306" t="n"/>
-      <c r="I33" s="97" t="n"/>
-      <c r="J33" s="230" t="n"/>
-      <c r="K33" s="98" t="n"/>
-      <c r="L33" s="97" t="n"/>
+      <c r="H33" s="370" t="n"/>
+      <c r="I33" s="371" t="n"/>
+      <c r="J33" s="372" t="n"/>
+      <c r="K33" s="373" t="n"/>
+      <c r="L33" s="371" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1" s="127">
-      <c r="A34" s="306" t="n">
+      <c r="A34" s="368" t="n">
         <v>17</v>
       </c>
-      <c r="B34" s="230" t="inlineStr">
+      <c r="B34" s="369" t="inlineStr">
         <is>
           <t>Reporte e investigación oportuna de accidentes e incidentes</t>
         </is>
@@ -3146,17 +3185,17 @@
       <c r="E34" s="98" t="n"/>
       <c r="F34" s="98" t="n"/>
       <c r="G34" s="97" t="n"/>
-      <c r="H34" s="306" t="n"/>
-      <c r="I34" s="97" t="n"/>
-      <c r="J34" s="230" t="n"/>
-      <c r="K34" s="98" t="n"/>
-      <c r="L34" s="97" t="n"/>
+      <c r="H34" s="370" t="n"/>
+      <c r="I34" s="371" t="n"/>
+      <c r="J34" s="372" t="n"/>
+      <c r="K34" s="373" t="n"/>
+      <c r="L34" s="371" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1" s="127">
-      <c r="A35" s="306" t="n">
+      <c r="A35" s="368" t="n">
         <v>18</v>
       </c>
-      <c r="B35" s="230" t="inlineStr">
+      <c r="B35" s="369" t="inlineStr">
         <is>
           <t>Reporte de actos y condiciones inseguras</t>
         </is>
@@ -3166,11 +3205,11 @@
       <c r="E35" s="98" t="n"/>
       <c r="F35" s="98" t="n"/>
       <c r="G35" s="97" t="n"/>
-      <c r="H35" s="306" t="n"/>
-      <c r="I35" s="97" t="n"/>
-      <c r="J35" s="230" t="n"/>
-      <c r="K35" s="98" t="n"/>
-      <c r="L35" s="97" t="n"/>
+      <c r="H35" s="370" t="n"/>
+      <c r="I35" s="371" t="n"/>
+      <c r="J35" s="372" t="n"/>
+      <c r="K35" s="373" t="n"/>
+      <c r="L35" s="371" t="n"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="127">
       <c r="A36" s="137" t="inlineStr">
@@ -3327,68 +3366,68 @@
       <c r="L41" s="348" t="n"/>
     </row>
     <row r="42" ht="24" customHeight="1" s="127">
-      <c r="A42" s="306" t="n">
+      <c r="A42" s="368" t="n">
         <v>1</v>
       </c>
-      <c r="B42" s="230" t="n"/>
-      <c r="C42" s="98" t="n"/>
-      <c r="D42" s="98" t="n"/>
-      <c r="E42" s="98" t="n"/>
-      <c r="F42" s="98" t="n"/>
-      <c r="G42" s="97" t="n"/>
-      <c r="H42" s="230" t="n"/>
-      <c r="I42" s="98" t="n"/>
-      <c r="J42" s="97" t="n"/>
-      <c r="K42" s="306" t="n"/>
-      <c r="L42" s="97" t="n"/>
+      <c r="B42" s="372" t="n"/>
+      <c r="C42" s="373" t="n"/>
+      <c r="D42" s="373" t="n"/>
+      <c r="E42" s="373" t="n"/>
+      <c r="F42" s="373" t="n"/>
+      <c r="G42" s="371" t="n"/>
+      <c r="H42" s="372" t="n"/>
+      <c r="I42" s="373" t="n"/>
+      <c r="J42" s="371" t="n"/>
+      <c r="K42" s="370" t="n"/>
+      <c r="L42" s="371" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1" s="127">
-      <c r="A43" s="306" t="n">
+      <c r="A43" s="368" t="n">
         <v>2</v>
       </c>
-      <c r="B43" s="230" t="n"/>
-      <c r="C43" s="98" t="n"/>
-      <c r="D43" s="98" t="n"/>
-      <c r="E43" s="98" t="n"/>
-      <c r="F43" s="98" t="n"/>
-      <c r="G43" s="97" t="n"/>
-      <c r="H43" s="230" t="n"/>
-      <c r="I43" s="98" t="n"/>
-      <c r="J43" s="97" t="n"/>
-      <c r="K43" s="306" t="n"/>
-      <c r="L43" s="97" t="n"/>
+      <c r="B43" s="372" t="n"/>
+      <c r="C43" s="373" t="n"/>
+      <c r="D43" s="373" t="n"/>
+      <c r="E43" s="373" t="n"/>
+      <c r="F43" s="373" t="n"/>
+      <c r="G43" s="371" t="n"/>
+      <c r="H43" s="372" t="n"/>
+      <c r="I43" s="373" t="n"/>
+      <c r="J43" s="371" t="n"/>
+      <c r="K43" s="370" t="n"/>
+      <c r="L43" s="371" t="n"/>
     </row>
     <row r="44" ht="24" customHeight="1" s="127">
-      <c r="A44" s="306" t="n">
+      <c r="A44" s="368" t="n">
         <v>3</v>
       </c>
-      <c r="B44" s="230" t="n"/>
-      <c r="C44" s="98" t="n"/>
-      <c r="D44" s="98" t="n"/>
-      <c r="E44" s="98" t="n"/>
-      <c r="F44" s="98" t="n"/>
-      <c r="G44" s="97" t="n"/>
-      <c r="H44" s="230" t="n"/>
-      <c r="I44" s="98" t="n"/>
-      <c r="J44" s="97" t="n"/>
-      <c r="K44" s="306" t="n"/>
-      <c r="L44" s="97" t="n"/>
+      <c r="B44" s="372" t="n"/>
+      <c r="C44" s="373" t="n"/>
+      <c r="D44" s="373" t="n"/>
+      <c r="E44" s="373" t="n"/>
+      <c r="F44" s="373" t="n"/>
+      <c r="G44" s="371" t="n"/>
+      <c r="H44" s="372" t="n"/>
+      <c r="I44" s="373" t="n"/>
+      <c r="J44" s="371" t="n"/>
+      <c r="K44" s="370" t="n"/>
+      <c r="L44" s="371" t="n"/>
     </row>
     <row r="45" ht="24" customHeight="1" s="127">
-      <c r="A45" s="306" t="n">
+      <c r="A45" s="368" t="n">
         <v>4</v>
       </c>
-      <c r="B45" s="230" t="n"/>
-      <c r="C45" s="98" t="n"/>
-      <c r="D45" s="98" t="n"/>
-      <c r="E45" s="98" t="n"/>
-      <c r="F45" s="98" t="n"/>
-      <c r="G45" s="97" t="n"/>
-      <c r="H45" s="230" t="n"/>
-      <c r="I45" s="98" t="n"/>
-      <c r="J45" s="97" t="n"/>
-      <c r="K45" s="306" t="n"/>
-      <c r="L45" s="97" t="n"/>
+      <c r="B45" s="372" t="n"/>
+      <c r="C45" s="373" t="n"/>
+      <c r="D45" s="373" t="n"/>
+      <c r="E45" s="373" t="n"/>
+      <c r="F45" s="373" t="n"/>
+      <c r="G45" s="371" t="n"/>
+      <c r="H45" s="372" t="n"/>
+      <c r="I45" s="373" t="n"/>
+      <c r="J45" s="371" t="n"/>
+      <c r="K45" s="370" t="n"/>
+      <c r="L45" s="371" t="n"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="127">
       <c r="A46" s="137" t="inlineStr">
@@ -3441,24 +3480,24 @@
         </is>
       </c>
       <c r="B48" s="97" t="n"/>
-      <c r="C48" s="301" t="n"/>
-      <c r="D48" s="97" t="n"/>
+      <c r="C48" s="372" t="n"/>
+      <c r="D48" s="371" t="n"/>
       <c r="E48" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F48" s="97" t="n"/>
-      <c r="G48" s="301" t="n"/>
-      <c r="H48" s="97" t="n"/>
+      <c r="G48" s="372" t="n"/>
+      <c r="H48" s="371" t="n"/>
       <c r="I48" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J48" s="97" t="n"/>
-      <c r="K48" s="301" t="n"/>
-      <c r="L48" s="97" t="n"/>
+      <c r="K48" s="372" t="n"/>
+      <c r="L48" s="371" t="n"/>
     </row>
     <row r="49" ht="21" customHeight="1" s="127">
       <c r="A49" s="302" t="inlineStr">
@@ -3467,24 +3506,24 @@
         </is>
       </c>
       <c r="B49" s="97" t="n"/>
-      <c r="C49" s="301" t="n"/>
-      <c r="D49" s="97" t="n"/>
+      <c r="C49" s="372" t="n"/>
+      <c r="D49" s="371" t="n"/>
       <c r="E49" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F49" s="97" t="n"/>
-      <c r="G49" s="301" t="n"/>
-      <c r="H49" s="97" t="n"/>
+      <c r="G49" s="372" t="n"/>
+      <c r="H49" s="371" t="n"/>
       <c r="I49" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J49" s="97" t="n"/>
-      <c r="K49" s="301" t="n"/>
-      <c r="L49" s="97" t="n"/>
+      <c r="K49" s="372" t="n"/>
+      <c r="L49" s="371" t="n"/>
     </row>
     <row r="50" ht="21" customHeight="1" s="127">
       <c r="A50" s="302" t="inlineStr">
@@ -3493,24 +3532,24 @@
         </is>
       </c>
       <c r="B50" s="97" t="n"/>
-      <c r="C50" s="301" t="n"/>
-      <c r="D50" s="97" t="n"/>
+      <c r="C50" s="372" t="n"/>
+      <c r="D50" s="371" t="n"/>
       <c r="E50" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F50" s="97" t="n"/>
-      <c r="G50" s="301" t="n"/>
-      <c r="H50" s="97" t="n"/>
+      <c r="G50" s="372" t="n"/>
+      <c r="H50" s="371" t="n"/>
       <c r="I50" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J50" s="97" t="n"/>
-      <c r="K50" s="301" t="n"/>
-      <c r="L50" s="97" t="n"/>
+      <c r="K50" s="372" t="n"/>
+      <c r="L50" s="371" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="25" t="inlineStr">
@@ -3524,6 +3563,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="140">
     <mergeCell ref="K49:L49"/>
     <mergeCell ref="H35:I35"/>
